--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.51555871441674</v>
+        <v>9.83377829109272</v>
       </c>
       <c r="D2" t="n">
-        <v>60.21887808544613</v>
+        <v>9.785567688884996</v>
       </c>
       <c r="E2" t="n">
-        <v>11.28380143921442</v>
+        <v>1.833617733872343</v>
       </c>
       <c r="F2" t="n">
-        <v>17.3951033642203</v>
+        <v>2.826704296685798</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.31079064826214</v>
+        <v>8.825503480342599</v>
       </c>
       <c r="D3" t="n">
-        <v>54.06396553107259</v>
+        <v>8.785394398799296</v>
       </c>
       <c r="E3" t="n">
-        <v>11.28380143921442</v>
+        <v>1.833617733872343</v>
       </c>
       <c r="F3" t="n">
-        <v>17.3951033642203</v>
+        <v>2.826704296685798</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.94009615014215</v>
+        <v>7.952765624398101</v>
       </c>
       <c r="D4" t="n">
-        <v>49.03932819264836</v>
+        <v>7.968890831305358</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28380143921442</v>
+        <v>1.833617733872343</v>
       </c>
       <c r="F4" t="n">
-        <v>17.3951033642203</v>
+        <v>2.826704296685798</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.82767908254687</v>
+        <v>4.684497850913866</v>
       </c>
       <c r="D5" t="n">
-        <v>29.17982639531725</v>
+        <v>4.741721789239053</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28380143921442</v>
+        <v>1.833617733872343</v>
       </c>
       <c r="F5" t="n">
-        <v>17.3951033642203</v>
+        <v>2.826704296685798</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.85854486176481</v>
+        <v>7.614513540036782</v>
       </c>
       <c r="D6" t="n">
-        <v>8.285788992628866</v>
+        <v>1.346440711302191</v>
       </c>
       <c r="E6" t="n">
-        <v>11.28380143921442</v>
+        <v>1.833617733872343</v>
       </c>
       <c r="F6" t="n">
-        <v>17.3951033642203</v>
+        <v>2.826704296685798</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>63.29605569977316</v>
+        <v>10.28560905121314</v>
       </c>
       <c r="D7" t="n">
-        <v>37.83715237432794</v>
+        <v>6.148537260828291</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28380143921442</v>
+        <v>1.833617733872343</v>
       </c>
       <c r="F7" t="n">
-        <v>17.3951033642203</v>
+        <v>2.826704296685798</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
